--- a/excel/100(n)/AVG_Random_Dataset.xlsx
+++ b/excel/100(n)/AVG_Random_Dataset.xlsx
@@ -102,19 +102,19 @@
         <v>100.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>102780.0</v>
+        <v>17127.3</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>47280.0</v>
+        <v>4580.9</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>42210.0</v>
+        <v>7965.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>18700.0</v>
+        <v>10841.7</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>20840.0</v>
+        <v>13178.8</v>
       </c>
     </row>
   </sheetData>
